--- a/B-6/Assets/Resources/Json/enemy/enemy_data.xlsx
+++ b/B-6/Assets/Resources/Json/enemy/enemy_data.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="47" documentId="11_6E8EAB6661E618BD64B32149CAC7046F2BCFF665" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20895C34-82D8-4394-A709-AD4F8CBE48A3}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6df029749d5c6239/デスクトップ/1009/B-6/Assets/Resources/Json/enemy/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="59" documentId="11_6E8EAB6661E618BD64B32149CAC7046F2BCFF665" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58948508-424F-4A75-B311-E66DA702F682}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,11 +63,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -70,8 +75,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -420,9 +432,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -445,7 +457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -468,7 +480,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -491,7 +503,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -514,7 +526,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -537,7 +549,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -545,7 +557,7 @@
         <v>20</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>1.2</v>
@@ -560,7 +572,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -568,7 +580,7 @@
         <v>20</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>1.2</v>
@@ -583,7 +595,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -591,7 +603,7 @@
         <v>20</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>1.2</v>
@@ -606,7 +618,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -614,7 +626,7 @@
         <v>20</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D9">
         <v>1.2</v>
@@ -629,38 +641,38 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="C10">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>1.2</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G10">
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D11">
         <v>1.2</v>
@@ -675,12 +687,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="C12">
         <v>20</v>
@@ -699,11 +711,23 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45e75c57-a883-4f1a-8e28-effa0a633cfd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100CA2EEB5C486BA448AC1B54B2E38D6833" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="a0e8d859f13fcc4ef53aae1bf113f035">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="45e75c57-a883-4f1a-8e28-effa0a633cfd" xmlns:ns3="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="748b9a06c6582f68083b9ca7ee3bd5aa" ns2:_="" ns3:_="">
     <xsd:import namespace="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
@@ -898,17 +922,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45e75c57-a883-4f1a-8e28-effa0a633cfd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -919,13 +932,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B99D8D32-D122-4962-8C59-C50F7265F223}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0A7E7A-B940-40D6-B4F2-FF40EF6B591F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
+    <ds:schemaRef ds:uri="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0A7E7A-B940-40D6-B4F2-FF40EF6B591F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B99D8D32-D122-4962-8C59-C50F7265F223}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
+    <ds:schemaRef ds:uri="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F9971E-2CB9-4355-B636-B2B93991C1DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F9971E-2CB9-4355-B636-B2B93991C1DA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/B-6/Assets/Resources/Json/enemy/enemy_data.xlsx
+++ b/B-6/Assets/Resources/Json/enemy/enemy_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6df029749d5c6239/デスクトップ/1009/B-6/Assets/Resources/Json/enemy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="11_6E8EAB6661E618BD64B32149CAC7046F2BCFF665" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58948508-424F-4A75-B311-E66DA702F682}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_6E8EAB6661E618BD64B32149CAC7046F2BCFF665" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2498C1A2-ECD5-41DC-B430-67DC98EAAFA2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -142,6 +142,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -600,7 +604,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -623,7 +627,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -655,10 +659,10 @@
         <v>1.2</v>
       </c>
       <c r="E10">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>0.5</v>
@@ -669,7 +673,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="C11">
         <v>20</v>
@@ -692,7 +696,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="C12">
         <v>20</v>
@@ -717,17 +721,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45e75c57-a883-4f1a-8e28-effa0a633cfd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100CA2EEB5C486BA448AC1B54B2E38D6833" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="a0e8d859f13fcc4ef53aae1bf113f035">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="45e75c57-a883-4f1a-8e28-effa0a633cfd" xmlns:ns3="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="748b9a06c6582f68083b9ca7ee3bd5aa" ns2:_="" ns3:_="">
     <xsd:import namespace="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
@@ -922,6 +915,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45e75c57-a883-4f1a-8e28-effa0a633cfd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -932,17 +936,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0A7E7A-B940-40D6-B4F2-FF40EF6B591F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
-    <ds:schemaRef ds:uri="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B99D8D32-D122-4962-8C59-C50F7265F223}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -961,6 +954,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0A7E7A-B940-40D6-B4F2-FF40EF6B591F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
+    <ds:schemaRef ds:uri="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F9971E-2CB9-4355-B636-B2B93991C1DA}">
   <ds:schemaRefs>

--- a/B-6/Assets/Resources/Json/enemy/enemy_data.xlsx
+++ b/B-6/Assets/Resources/Json/enemy/enemy_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6df029749d5c6239/デスクトップ/1009/B-6/Assets/Resources/Json/enemy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="11_6E8EAB6661E618BD64B32149CAC7046F2BCFF665" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2498C1A2-ECD5-41DC-B430-67DC98EAAFA2}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_6E8EAB6661E618BD64B32149CAC7046F2BCFF665" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{913D6046-7A3E-43C5-91C3-3F2A351968D4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -659,13 +659,13 @@
         <v>1.2</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F10">
         <v>10</v>
       </c>
       <c r="G10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -688,7 +688,7 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -711,7 +711,7 @@
         <v>8</v>
       </c>
       <c r="G12">
-        <v>0.5</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -721,6 +721,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45e75c57-a883-4f1a-8e28-effa0a633cfd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100CA2EEB5C486BA448AC1B54B2E38D6833" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="a0e8d859f13fcc4ef53aae1bf113f035">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="45e75c57-a883-4f1a-8e28-effa0a633cfd" xmlns:ns3="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="748b9a06c6582f68083b9ca7ee3bd5aa" ns2:_="" ns3:_="">
     <xsd:import namespace="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
@@ -915,17 +926,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45e75c57-a883-4f1a-8e28-effa0a633cfd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -936,6 +936,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0A7E7A-B940-40D6-B4F2-FF40EF6B591F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
+    <ds:schemaRef ds:uri="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B99D8D32-D122-4962-8C59-C50F7265F223}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -954,17 +965,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0A7E7A-B940-40D6-B4F2-FF40EF6B591F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
-    <ds:schemaRef ds:uri="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F9971E-2CB9-4355-B636-B2B93991C1DA}">
   <ds:schemaRefs>
